--- a/excel/TRT_Word_KOR.xlsx
+++ b/excel/TRT_Word_KOR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\classification-main\classification-main\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{360BB484-98DE-4C13-9017-0F24D0BB6A28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A4D3305-C15A-4AB6-94B0-D943EEB14878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{74BD6AE7-1D9C-4ADB-9E4F-52195803F6A8}"/>
+    <workbookView xWindow="4815" yWindow="3195" windowWidth="28800" windowHeight="15255" xr2:uid="{74BD6AE7-1D9C-4ADB-9E4F-52195803F6A8}"/>
   </bookViews>
   <sheets>
     <sheet name="TRT_Word_KOR" sheetId="1" r:id="rId1"/>
@@ -431,592 +431,617 @@
     <t>[T, AA1, P]</t>
   </si>
   <si>
+    <t>[B, AE1, K]</t>
+  </si>
+  <si>
+    <t>[1, 8, 3]</t>
+  </si>
+  <si>
+    <t>[G, OW1]</t>
+  </si>
+  <si>
+    <t>[3, 10]</t>
+  </si>
+  <si>
+    <t>[AH1, P]</t>
+  </si>
+  <si>
+    <t>[9, 1]</t>
+  </si>
+  <si>
+    <t>[M, AE1, P]</t>
+  </si>
+  <si>
+    <t>[SH, OW1]</t>
+  </si>
+  <si>
+    <t>[4, 10]</t>
+  </si>
+  <si>
+    <t>[HH, AA1, T]</t>
+  </si>
+  <si>
+    <t>[T, IY1, V, IY1]</t>
+  </si>
+  <si>
+    <t>[2, 7, 5, 7]</t>
+  </si>
+  <si>
+    <t>[V, AA1, L, Y, UW0, M]</t>
+  </si>
+  <si>
+    <t>[5, 9, 3, 3, 11, 1]</t>
+  </si>
+  <si>
+    <t>[S, EH1, N, T, ER0]</t>
+  </si>
+  <si>
+    <t>[EH1, L, B, AH0, M]</t>
+  </si>
+  <si>
+    <t>[8, 3, 1, 9, 1]</t>
+  </si>
+  <si>
+    <t>[K, AH0, F, EY1]</t>
+  </si>
+  <si>
+    <t>[3, 9, 5, 8]</t>
+  </si>
+  <si>
+    <t>[N, UW1, Z]</t>
+  </si>
+  <si>
+    <t>[3, 11, 2]</t>
+  </si>
+  <si>
+    <t>[K, AH1, L, ER0]</t>
+  </si>
+  <si>
+    <t>[3, 9, 3, 12]</t>
+  </si>
+  <si>
+    <t>[T, AE1, K, S, IY0]</t>
+  </si>
+  <si>
+    <t>[2, 8, 3, 2, 7]</t>
+  </si>
+  <si>
+    <t>[B, AH1, S]</t>
+  </si>
+  <si>
+    <t>[1, 9, 2]</t>
+  </si>
+  <si>
+    <t>[M, AH1, N, IY0]</t>
+  </si>
+  <si>
+    <t>[1, 9, 3, 7]</t>
+  </si>
+  <si>
+    <t>[T, AH1, CH]</t>
+  </si>
+  <si>
+    <t>[2, 9, 4]</t>
+  </si>
+  <si>
+    <t>[T, IH1, K, AH0, T]</t>
+  </si>
+  <si>
+    <t>[2, 7, 3, 9, 2]</t>
+  </si>
+  <si>
+    <t>[HH, IY1, T, ER0]</t>
+  </si>
+  <si>
+    <t>[3, 7, 2, 12]</t>
+  </si>
+  <si>
+    <t>[K, UW1, P, AO2, N]</t>
+  </si>
+  <si>
+    <t>[3, 11, 1, 10, 3]</t>
+  </si>
+  <si>
+    <t>[F, OW1, L, D, ER0]</t>
+  </si>
+  <si>
+    <t>[5, 10, 3, 2, 12]</t>
+  </si>
+  <si>
+    <t>[R, EY1, D, IY0, OW2]</t>
+  </si>
+  <si>
+    <t>[6, 8, 2, 7, 10]</t>
+  </si>
+  <si>
+    <t>[K, IY1, B, AO2, R, D]</t>
+  </si>
+  <si>
+    <t>[3, 7, 1, 10, 6, 2]</t>
+  </si>
+  <si>
+    <t>[M, AW1, S]</t>
+  </si>
+  <si>
+    <t>[IH1, N, D, EH0, K, S]</t>
+  </si>
+  <si>
+    <t>[7, 3, 2, 8, 3, 2]</t>
+  </si>
+  <si>
+    <t>[P, R, IH1, N, T]</t>
+  </si>
+  <si>
+    <t>[1, 6, 7, 3, 2]</t>
+  </si>
+  <si>
+    <t>[S, P, IY1, K, ER0]</t>
+  </si>
+  <si>
+    <t>[2, 1, 7, 3, 12]</t>
+  </si>
+  <si>
+    <t>[K, AE1, M, ER0, AH0]</t>
+  </si>
+  <si>
+    <t>[3, 8, 1, 12, 9]</t>
+  </si>
+  <si>
+    <t>[IH1, N, T, ER0, N, EH2, T]</t>
+  </si>
+  <si>
+    <t>[IY0, M, EY1, L]</t>
+  </si>
+  <si>
+    <t>[M, AA1, N, AH0, T, ER0]</t>
+  </si>
+  <si>
+    <t>[1, 9, 3, 9, 2, 12]</t>
+  </si>
+  <si>
+    <t>[M, AY1, K]</t>
+  </si>
+  <si>
+    <t>[K, AE1, M, P, AH0, S]</t>
+  </si>
+  <si>
+    <t>[D, EY1, T, AH0]</t>
+  </si>
+  <si>
+    <t>[2, 8, 2, 9]</t>
+  </si>
+  <si>
+    <t>[V, IH1, D, IY0, OW0]</t>
+  </si>
+  <si>
+    <t>[5, 7, 2, 7, 10]</t>
+  </si>
+  <si>
+    <t>[W, IH1, N, D, OW0]</t>
+  </si>
+  <si>
+    <t>[6, 7, 3, 2, 10]</t>
+  </si>
+  <si>
+    <t>[S, AH0, P, AO1, R, T]</t>
+  </si>
+  <si>
+    <t>[2, 9, 1, 10, 6, 2]</t>
+  </si>
+  <si>
+    <t>[S, M, AA1, R, T, F, OW2, N]</t>
+  </si>
+  <si>
+    <t>[2, 1, 9, 6, 2, 5, 10, 3]</t>
+  </si>
+  <si>
+    <t>[B, L, UW1, T, UW2, TH]</t>
+  </si>
+  <si>
+    <t>[1, 3, 11, 2, 11, 2]</t>
+  </si>
+  <si>
+    <t>[AE0, K, S, EH1, S, ER0, IY0]</t>
+  </si>
+  <si>
+    <t>[8, 3, 2, 8, 2, 12, 7]</t>
+  </si>
+  <si>
+    <t>[IH1, N, S, AY2, T]</t>
+  </si>
+  <si>
+    <t>[P, R, AH0, M, OW1, SH, AH0, N]</t>
+  </si>
+  <si>
+    <t>[1, 6, 9, 1, 10, 4, 9, 3]</t>
+  </si>
+  <si>
+    <t>[W, AY1, F, IY0]</t>
+  </si>
+  <si>
+    <t>[6, 9, 5, 7]</t>
+  </si>
+  <si>
+    <t>[K, AE1, T, AH0, G, AO2, R, IY0]</t>
+  </si>
+  <si>
+    <t>[3, 8, 2, 9, 3, 10, 6, 7]</t>
+  </si>
+  <si>
+    <t>[D, IH0, L, IH1, V, ER0, IY0]</t>
+  </si>
+  <si>
+    <t>[2, 7, 3, 7, 5, 12, 7]</t>
+  </si>
+  <si>
+    <t>[P, R, OW1, G, R, AE2, M]</t>
+  </si>
+  <si>
+    <t>[1, 6, 10, 3, 6, 8, 1]</t>
+  </si>
+  <si>
+    <t>[K, AH0, M, Y, UW1, N, AH0, T, IY0]</t>
+  </si>
+  <si>
+    <t>[3, 9, 1, 3, 11, 3, 9, 2, 7]</t>
+  </si>
+  <si>
+    <t>[D, AW1, N, L, OW2, D]</t>
+  </si>
+  <si>
+    <t>[2, 9, 3, 3, 10, 2]</t>
+  </si>
+  <si>
+    <t>[P, R, AA1, JH, EH0, K, T]</t>
+  </si>
+  <si>
+    <t>[1, 6, 9, 4, 8, 3, 2]</t>
+  </si>
+  <si>
+    <t>[AH0, K, AE1, D, AH0, M, IY0]</t>
+  </si>
+  <si>
+    <t>[9, 3, 8, 2, 9, 1, 7]</t>
+  </si>
+  <si>
+    <t>[V, Y, UW1]</t>
+  </si>
+  <si>
+    <t>[K, IY1]</t>
+  </si>
+  <si>
+    <t>[AH0, L, AA1, R, M]</t>
+  </si>
+  <si>
+    <t>[M, AA1, R, K, AH0, T]</t>
+  </si>
+  <si>
+    <t>[1, 9, 6, 3, 9, 2]</t>
+  </si>
+  <si>
+    <t>[D, AW1, N]</t>
+  </si>
+  <si>
+    <t>[2, 9, 3]</t>
+  </si>
+  <si>
+    <t>[P, AW1, ER0]</t>
+  </si>
+  <si>
+    <t>[1, 9, 12]</t>
+  </si>
+  <si>
+    <t>[P, AA1, R, K]</t>
+  </si>
+  <si>
+    <t>[M, EH1, N, Y, UW0]</t>
+  </si>
+  <si>
+    <t>[1, 8, 3, 3, 11]</t>
+  </si>
+  <si>
+    <t>[L, AE1, M, P]</t>
+  </si>
+  <si>
+    <t>[3, 8, 1, 1]</t>
+  </si>
+  <si>
+    <t>[HH, OW0, T, EH1, L]</t>
+  </si>
+  <si>
+    <t>[3, 10, 2, 8, 3]</t>
+  </si>
+  <si>
+    <t>[M, Y, UW1, Z, IH0, K]</t>
+  </si>
+  <si>
+    <t>[1, 3, 11, 2, 7, 3]</t>
+  </si>
+  <si>
+    <t>[W, AO1, L, AH0, T]</t>
+  </si>
+  <si>
+    <t>[W, EH1, DH, ER0]</t>
+  </si>
+  <si>
+    <t>[6, 8, 2, 12]</t>
+  </si>
+  <si>
+    <t>[S, T, AA1, P]</t>
+  </si>
+  <si>
+    <t>[2, 2, 9, 1]</t>
+  </si>
+  <si>
+    <t>[S, K, UW1, L]</t>
+  </si>
+  <si>
+    <t>[2, 3, 11, 3]</t>
+  </si>
+  <si>
+    <t>[T, R, IY1]</t>
+  </si>
+  <si>
+    <t>[F, IH1, L, M]</t>
+  </si>
+  <si>
+    <t>[5, 7, 3, 1]</t>
+  </si>
+  <si>
+    <t>[IH1, D]</t>
+  </si>
+  <si>
+    <t>[7, 2]</t>
+  </si>
+  <si>
+    <t>[T, EH1, L, AH0, F, OW2, N]</t>
+  </si>
+  <si>
+    <t>[2, 8, 3, 9, 5, 10, 3]</t>
+  </si>
+  <si>
+    <t>[S, AH0, L, EH1, K, T]</t>
+  </si>
+  <si>
+    <t>[2, 9, 3, 8, 3, 2]</t>
+  </si>
+  <si>
+    <t>[M, AE1, G, AH0, Z, IY2, N]</t>
+  </si>
+  <si>
+    <t>[1, 8, 3, 9, 2, 7, 3]</t>
+  </si>
+  <si>
+    <t>[S, EY1, V]</t>
+  </si>
+  <si>
+    <t>[2, 8, 5]</t>
+  </si>
+  <si>
+    <t>[M, EH1, S, AH0, JH]</t>
+  </si>
+  <si>
+    <t>[K, AH0, M, P, Y, UW1, T, ER0]</t>
+  </si>
+  <si>
+    <t>[3, 9, 1, 1, 3, 11, 2, 12]</t>
+  </si>
+  <si>
+    <t>[K, AH0, N, D, IH1, SH, AH0, N]</t>
+  </si>
+  <si>
+    <t>[3, 9, 3, 2, 7, 4, 9, 3]</t>
+  </si>
+  <si>
+    <t>[D, AO1, R, L, AH0, K]</t>
+  </si>
+  <si>
+    <t>[F, AO1, R, W, ER0, D]</t>
+  </si>
+  <si>
+    <t>[5, 10, 6, 6, 12, 2]</t>
+  </si>
+  <si>
+    <t>[AO1, F, AH0, S]</t>
+  </si>
+  <si>
+    <t>[10, 5, 9, 2]</t>
+  </si>
+  <si>
+    <t>[B, UH1, K, M, AA0, R, K]</t>
+  </si>
+  <si>
+    <t>[1, 11, 3, 1, 9, 6, 3]</t>
+  </si>
+  <si>
+    <t>[P, L, EY1]</t>
+  </si>
+  <si>
+    <t>[1, 3, 8]</t>
+  </si>
+  <si>
+    <t>[B, R, AH1, SH]</t>
+  </si>
+  <si>
+    <t>[1, 6, 9, 4]</t>
+  </si>
+  <si>
+    <t>[S, T, AH1, D, IY0]</t>
+  </si>
+  <si>
+    <t>[2, 2, 9, 2, 7]</t>
+  </si>
+  <si>
+    <t>[L, IH1, S, T]</t>
+  </si>
+  <si>
+    <t>[3, 7, 2, 2]</t>
+  </si>
+  <si>
+    <t>[AY0, D, IY1, AH0]</t>
+  </si>
+  <si>
+    <t>[P, AE1, S, W, ER2, D]</t>
+  </si>
+  <si>
+    <t>[AE0, K, T, IH1, V, AH0, T, IY0]</t>
+  </si>
+  <si>
+    <t>[8, 3, 2, 7, 5, 9, 2, 7]</t>
+  </si>
+  <si>
+    <t>[S, AH1, B, W, EY2]</t>
+  </si>
+  <si>
+    <t>[S, K, R, IY1, N, SH, AH0, T]</t>
+  </si>
+  <si>
+    <t>[IH0, M, ER1, JH, AH0, N, S, IY0]</t>
+  </si>
+  <si>
+    <t>[R, IY1, W, AY0, N, D]</t>
+  </si>
+  <si>
+    <t>[6, 7, 6, 9, 3, 2]</t>
+  </si>
+  <si>
+    <t>[S, ER1, V, ER0]</t>
+  </si>
+  <si>
+    <t>[2, 12, 5, 12]</t>
+  </si>
+  <si>
+    <t>[OW1, P, AH0, N]</t>
+  </si>
+  <si>
+    <t>[10, 1, 9, 3]</t>
+  </si>
+  <si>
+    <t>[W, ER1, K]</t>
+  </si>
+  <si>
+    <t>[V, IY1, Z, AH0]</t>
+  </si>
+  <si>
+    <t>[5, 7, 2, 9]</t>
+  </si>
+  <si>
+    <t>[K, L, OW1, S]</t>
+  </si>
+  <si>
+    <t>[3, 3, 10, 2]</t>
+  </si>
+  <si>
+    <t>[F, EH1, S, T, AH0, V, AH0, L]</t>
+  </si>
+  <si>
+    <t>[M, EY1, K, AH2, P]</t>
+  </si>
+  <si>
+    <t>[1, 8, 3, 9, 1]</t>
+  </si>
+  <si>
+    <t>[EH1, N, JH, AH0, N, IH1, R]</t>
+  </si>
+  <si>
+    <t>[2, 8, 3, 2, 12]</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>[7, 1, 12, 4, 9, 3, 2, 7]</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>[5, 8, 2, 2, 9, 5, 9, 3]</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>[2, 3, 6, 7, 3, 4, 9, 2]</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>[1, 8, 2, 9, 4]</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>[1, 8, 2, 6, 12, 2]</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>[6, 12, 3]</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>[7, 1, 8, 3]</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>[2, 9, 1, 6, 8]</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>[7, 3, 2, 12, 3, 8, 2]</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>[9, 2, 7, 9]</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>[8, 3, 4, 9, 3, 7, 6]</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>[3, 8, 1, 1, 9, 2]</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>[1, 9, 6, 3]</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>[1, 9, 3]</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>[7, 3, 2, 9, 2]</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>[2, 9, 1]</t>
-  </si>
-  <si>
-    <t>[B, AE1, K]</t>
-  </si>
-  <si>
-    <t>[1, 8, 3]</t>
-  </si>
-  <si>
-    <t>[G, OW1]</t>
-  </si>
-  <si>
-    <t>[3, 10]</t>
-  </si>
-  <si>
-    <t>[AH1, P]</t>
-  </si>
-  <si>
-    <t>[9, 1]</t>
-  </si>
-  <si>
-    <t>[M, AE1, P]</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>[5, 3, 11]</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>[2, 10, 6, 3, 9, 3]</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>[6, 10, 3, 9, 2]</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>[2, 6, 7]</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>[3, 9, 2]</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>[9, 3, 9, 6, 1]</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>[1, 8, 1]</t>
-  </si>
-  <si>
-    <t>[SH, OW1]</t>
-  </si>
-  <si>
-    <t>[4, 10]</t>
-  </si>
-  <si>
-    <t>[HH, AA1, T]</t>
-  </si>
-  <si>
-    <t>[3, 9, 2]</t>
-  </si>
-  <si>
-    <t>[T, IY1, V, IY1]</t>
-  </si>
-  <si>
-    <t>[2, 7, 5, 7]</t>
-  </si>
-  <si>
-    <t>[V, AA1, L, Y, UW0, M]</t>
-  </si>
-  <si>
-    <t>[5, 9, 3, 3, 11, 1]</t>
-  </si>
-  <si>
-    <t>[S, EH1, N, T, ER0]</t>
-  </si>
-  <si>
-    <t>[2, 8, 3, 2, 12]</t>
-  </si>
-  <si>
-    <t>[EH1, L, B, AH0, M]</t>
-  </si>
-  <si>
-    <t>[8, 3, 1, 9, 1]</t>
-  </si>
-  <si>
-    <t>[K, AH0, F, EY1]</t>
-  </si>
-  <si>
-    <t>[3, 9, 5, 8]</t>
-  </si>
-  <si>
-    <t>[N, UW1, Z]</t>
-  </si>
-  <si>
-    <t>[3, 11, 2]</t>
-  </si>
-  <si>
-    <t>[K, AH1, L, ER0]</t>
-  </si>
-  <si>
-    <t>[3, 9, 3, 12]</t>
-  </si>
-  <si>
-    <t>[T, AE1, K, S, IY0]</t>
-  </si>
-  <si>
-    <t>[2, 8, 3, 2, 7]</t>
-  </si>
-  <si>
-    <t>[B, AH1, S]</t>
-  </si>
-  <si>
-    <t>[1, 9, 2]</t>
-  </si>
-  <si>
-    <t>[M, AH1, N, IY0]</t>
-  </si>
-  <si>
-    <t>[1, 9, 3, 7]</t>
-  </si>
-  <si>
-    <t>[T, AH1, CH]</t>
-  </si>
-  <si>
-    <t>[2, 9, 4]</t>
-  </si>
-  <si>
-    <t>[T, IH1, K, AH0, T]</t>
-  </si>
-  <si>
-    <t>[2, 7, 3, 9, 2]</t>
-  </si>
-  <si>
-    <t>[HH, IY1, T, ER0]</t>
-  </si>
-  <si>
-    <t>[3, 7, 2, 12]</t>
-  </si>
-  <si>
-    <t>[K, UW1, P, AO2, N]</t>
-  </si>
-  <si>
-    <t>[3, 11, 1, 10, 3]</t>
-  </si>
-  <si>
-    <t>[F, OW1, L, D, ER0]</t>
-  </si>
-  <si>
-    <t>[5, 10, 3, 2, 12]</t>
-  </si>
-  <si>
-    <t>[R, EY1, D, IY0, OW2]</t>
-  </si>
-  <si>
-    <t>[6, 8, 2, 7, 10]</t>
-  </si>
-  <si>
-    <t>[K, IY1, B, AO2, R, D]</t>
-  </si>
-  <si>
-    <t>[3, 7, 1, 10, 6, 2]</t>
-  </si>
-  <si>
-    <t>[M, AW1, S]</t>
-  </si>
-  <si>
-    <t>[IH1, N, D, EH0, K, S]</t>
-  </si>
-  <si>
-    <t>[7, 3, 2, 8, 3, 2]</t>
-  </si>
-  <si>
-    <t>[P, R, IH1, N, T]</t>
-  </si>
-  <si>
-    <t>[1, 6, 7, 3, 2]</t>
-  </si>
-  <si>
-    <t>[S, P, IY1, K, ER0]</t>
-  </si>
-  <si>
-    <t>[2, 1, 7, 3, 12]</t>
-  </si>
-  <si>
-    <t>[K, AE1, M, ER0, AH0]</t>
-  </si>
-  <si>
-    <t>[3, 8, 1, 12, 9]</t>
-  </si>
-  <si>
-    <t>[IH1, N, T, ER0, N, EH2, T]</t>
-  </si>
-  <si>
-    <t>[7, 3, 2, 12, 3, 8, 2]</t>
-  </si>
-  <si>
-    <t>[IY0, M, EY1, L]</t>
-  </si>
-  <si>
-    <t>[7, 1, 8, 3]</t>
-  </si>
-  <si>
-    <t>[M, AA1, N, AH0, T, ER0]</t>
-  </si>
-  <si>
-    <t>[1, 9, 3, 9, 2, 12]</t>
-  </si>
-  <si>
-    <t>[M, AY1, K]</t>
-  </si>
-  <si>
-    <t>[1, 9, 3]</t>
-  </si>
-  <si>
-    <t>[K, AE1, M, P, AH0, S]</t>
-  </si>
-  <si>
-    <t>[3, 8, 1, 1, 9, 2]</t>
-  </si>
-  <si>
-    <t>[D, EY1, T, AH0]</t>
-  </si>
-  <si>
-    <t>[2, 8, 2, 9]</t>
-  </si>
-  <si>
-    <t>[V, IH1, D, IY0, OW0]</t>
-  </si>
-  <si>
-    <t>[5, 7, 2, 7, 10]</t>
-  </si>
-  <si>
-    <t>[W, IH1, N, D, OW0]</t>
-  </si>
-  <si>
-    <t>[6, 7, 3, 2, 10]</t>
-  </si>
-  <si>
-    <t>[S, AH0, P, AO1, R, T]</t>
-  </si>
-  <si>
-    <t>[2, 9, 1, 10, 6, 2]</t>
-  </si>
-  <si>
-    <t>[S, M, AA1, R, T, F, OW2, N]</t>
-  </si>
-  <si>
-    <t>[2, 1, 9, 6, 2, 5, 10, 3]</t>
-  </si>
-  <si>
-    <t>[B, L, UW1, T, UW2, TH]</t>
-  </si>
-  <si>
-    <t>[1, 3, 11, 2, 11, 2]</t>
-  </si>
-  <si>
-    <t>[AE0, K, S, EH1, S, ER0, IY0]</t>
-  </si>
-  <si>
-    <t>[8, 3, 2, 8, 2, 12, 7]</t>
-  </si>
-  <si>
-    <t>[IH1, N, S, AY2, T]</t>
-  </si>
-  <si>
-    <t>[7, 3, 2, 9, 2]</t>
-  </si>
-  <si>
-    <t>[P, R, AH0, M, OW1, SH, AH0, N]</t>
-  </si>
-  <si>
-    <t>[1, 6, 9, 1, 10, 4, 9, 3]</t>
-  </si>
-  <si>
-    <t>[W, AY1, F, IY0]</t>
-  </si>
-  <si>
-    <t>[6, 9, 5, 7]</t>
-  </si>
-  <si>
-    <t>[K, AE1, T, AH0, G, AO2, R, IY0]</t>
-  </si>
-  <si>
-    <t>[3, 8, 2, 9, 3, 10, 6, 7]</t>
-  </si>
-  <si>
-    <t>[D, IH0, L, IH1, V, ER0, IY0]</t>
-  </si>
-  <si>
-    <t>[2, 7, 3, 7, 5, 12, 7]</t>
-  </si>
-  <si>
-    <t>[P, R, OW1, G, R, AE2, M]</t>
-  </si>
-  <si>
-    <t>[1, 6, 10, 3, 6, 8, 1]</t>
-  </si>
-  <si>
-    <t>[K, AH0, M, Y, UW1, N, AH0, T, IY0]</t>
-  </si>
-  <si>
-    <t>[3, 9, 1, 3, 11, 3, 9, 2, 7]</t>
-  </si>
-  <si>
-    <t>[D, AW1, N, L, OW2, D]</t>
-  </si>
-  <si>
-    <t>[2, 9, 3, 3, 10, 2]</t>
-  </si>
-  <si>
-    <t>[P, R, AA1, JH, EH0, K, T]</t>
-  </si>
-  <si>
-    <t>[1, 6, 9, 4, 8, 3, 2]</t>
-  </si>
-  <si>
-    <t>[AH0, K, AE1, D, AH0, M, IY0]</t>
-  </si>
-  <si>
-    <t>[9, 3, 8, 2, 9, 1, 7]</t>
-  </si>
-  <si>
-    <t>[V, Y, UW1]</t>
-  </si>
-  <si>
-    <t>[5, 3, 11]</t>
-  </si>
-  <si>
-    <t>[K, IY1]</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>[3, 7]</t>
-  </si>
-  <si>
-    <t>[AH0, L, AA1, R, M]</t>
-  </si>
-  <si>
-    <t>[9, 3, 9, 6, 1]</t>
-  </si>
-  <si>
-    <t>[M, AA1, R, K, AH0, T]</t>
-  </si>
-  <si>
-    <t>[1, 9, 6, 3, 9, 2]</t>
-  </si>
-  <si>
-    <t>[D, AW1, N]</t>
-  </si>
-  <si>
-    <t>[2, 9, 3]</t>
-  </si>
-  <si>
-    <t>[P, AW1, ER0]</t>
-  </si>
-  <si>
-    <t>[1, 9, 12]</t>
-  </si>
-  <si>
-    <t>[P, AA1, R, K]</t>
-  </si>
-  <si>
-    <t>[1, 9, 6, 3]</t>
-  </si>
-  <si>
-    <t>[M, EH1, N, Y, UW0]</t>
-  </si>
-  <si>
-    <t>[1, 8, 3, 3, 11]</t>
-  </si>
-  <si>
-    <t>[L, AE1, M, P]</t>
-  </si>
-  <si>
-    <t>[3, 8, 1, 1]</t>
-  </si>
-  <si>
-    <t>[HH, OW0, T, EH1, L]</t>
-  </si>
-  <si>
-    <t>[3, 10, 2, 8, 3]</t>
-  </si>
-  <si>
-    <t>[M, Y, UW1, Z, IH0, K]</t>
-  </si>
-  <si>
-    <t>[1, 3, 11, 2, 7, 3]</t>
-  </si>
-  <si>
-    <t>[W, AO1, L, AH0, T]</t>
-  </si>
-  <si>
-    <t>[6, 10, 3, 9, 2]</t>
-  </si>
-  <si>
-    <t>[W, EH1, DH, ER0]</t>
-  </si>
-  <si>
-    <t>[6, 8, 2, 12]</t>
-  </si>
-  <si>
-    <t>[S, T, AA1, P]</t>
-  </si>
-  <si>
-    <t>[2, 2, 9, 1]</t>
-  </si>
-  <si>
-    <t>[S, K, UW1, L]</t>
-  </si>
-  <si>
-    <t>[2, 3, 11, 3]</t>
-  </si>
-  <si>
-    <t>[T, R, IY1]</t>
-  </si>
-  <si>
-    <t>[2, 6, 7]</t>
-  </si>
-  <si>
-    <t>[F, IH1, L, M]</t>
-  </si>
-  <si>
-    <t>[5, 7, 3, 1]</t>
-  </si>
-  <si>
-    <t>[IH1, D]</t>
-  </si>
-  <si>
-    <t>[7, 2]</t>
-  </si>
-  <si>
-    <t>[T, EH1, L, AH0, F, OW2, N]</t>
-  </si>
-  <si>
-    <t>[2, 8, 3, 9, 5, 10, 3]</t>
-  </si>
-  <si>
-    <t>[S, AH0, L, EH1, K, T]</t>
-  </si>
-  <si>
-    <t>[2, 9, 3, 8, 3, 2]</t>
-  </si>
-  <si>
-    <t>[M, AE1, G, AH0, Z, IY2, N]</t>
-  </si>
-  <si>
-    <t>[1, 8, 3, 9, 2, 7, 3]</t>
-  </si>
-  <si>
-    <t>[S, EY1, V]</t>
-  </si>
-  <si>
-    <t>[2, 8, 5]</t>
-  </si>
-  <si>
-    <t>[M, EH1, S, AH0, JH]</t>
-  </si>
-  <si>
-    <t>[1, 8, 2, 9, 4]</t>
-  </si>
-  <si>
-    <t>[K, AH0, M, P, Y, UW1, T, ER0]</t>
-  </si>
-  <si>
-    <t>[3, 9, 1, 1, 3, 11, 2, 12]</t>
-  </si>
-  <si>
-    <t>[K, AH0, N, D, IH1, SH, AH0, N]</t>
-  </si>
-  <si>
-    <t>[3, 9, 3, 2, 7, 4, 9, 3]</t>
-  </si>
-  <si>
-    <t>[D, AO1, R, L, AH0, K]</t>
-  </si>
-  <si>
-    <t>[2, 10, 6, 3, 9, 3]</t>
-  </si>
-  <si>
-    <t>[F, AO1, R, W, ER0, D]</t>
-  </si>
-  <si>
-    <t>[5, 10, 6, 6, 12, 2]</t>
-  </si>
-  <si>
-    <t>[AO1, F, AH0, S]</t>
-  </si>
-  <si>
-    <t>[10, 5, 9, 2]</t>
-  </si>
-  <si>
-    <t>[B, UH1, K, M, AA0, R, K]</t>
-  </si>
-  <si>
-    <t>[1, 11, 3, 1, 9, 6, 3]</t>
-  </si>
-  <si>
-    <t>[P, L, EY1]</t>
-  </si>
-  <si>
-    <t>[1, 3, 8]</t>
-  </si>
-  <si>
-    <t>[B, R, AH1, SH]</t>
-  </si>
-  <si>
-    <t>[1, 6, 9, 4]</t>
-  </si>
-  <si>
-    <t>[S, T, AH1, D, IY0]</t>
-  </si>
-  <si>
-    <t>[2, 2, 9, 2, 7]</t>
-  </si>
-  <si>
-    <t>[L, IH1, S, T]</t>
-  </si>
-  <si>
-    <t>[3, 7, 2, 2]</t>
-  </si>
-  <si>
-    <t>[AY0, D, IY1, AH0]</t>
-  </si>
-  <si>
-    <t>[9, 2, 7, 9]</t>
-  </si>
-  <si>
-    <t>[P, AE1, S, W, ER2, D]</t>
-  </si>
-  <si>
-    <t>[1, 8, 2, 6, 12, 2]</t>
-  </si>
-  <si>
-    <t>[AE0, K, T, IH1, V, AH0, T, IY0]</t>
-  </si>
-  <si>
-    <t>[8, 3, 2, 7, 5, 9, 2, 7]</t>
-  </si>
-  <si>
-    <t>[S, AH1, B, W, EY2]</t>
-  </si>
-  <si>
-    <t>[2, 9, 1, 6, 8]</t>
-  </si>
-  <si>
-    <t>[S, K, R, IY1, N, SH, AH0, T]</t>
-  </si>
-  <si>
-    <t>[2, 3, 6, 7, 3, 4, 9, 2]</t>
-  </si>
-  <si>
-    <t>[IH0, M, ER1, JH, AH0, N, S, IY0]</t>
-  </si>
-  <si>
-    <t>[7, 1, 12, 4, 9, 3, 2, 7]</t>
-  </si>
-  <si>
-    <t>[R, IY1, W, AY0, N, D]</t>
-  </si>
-  <si>
-    <t>[6, 7, 6, 9, 3, 2]</t>
-  </si>
-  <si>
-    <t>[S, ER1, V, ER0]</t>
-  </si>
-  <si>
-    <t>[2, 12, 5, 12]</t>
-  </si>
-  <si>
-    <t>[OW1, P, AH0, N]</t>
-  </si>
-  <si>
-    <t>[10, 1, 9, 3]</t>
-  </si>
-  <si>
-    <t>[W, ER1, K]</t>
-  </si>
-  <si>
-    <t>[6, 12, 3]</t>
-  </si>
-  <si>
-    <t>[V, IY1, Z, AH0]</t>
-  </si>
-  <si>
-    <t>[5, 7, 2, 9]</t>
-  </si>
-  <si>
-    <t>[K, L, OW1, S]</t>
-  </si>
-  <si>
-    <t>[3, 3, 10, 2]</t>
-  </si>
-  <si>
-    <t>[F, EH1, S, T, AH0, V, AH0, L]</t>
-  </si>
-  <si>
-    <t>[5, 8, 2, 2, 9, 5, 9, 3]</t>
-  </si>
-  <si>
-    <t>[M, EY1, K, AH2, P]</t>
-  </si>
-  <si>
-    <t>[1, 8, 3, 9, 1]</t>
-  </si>
-  <si>
-    <t>[EH1, N, JH, AH0, N, IH1, R]</t>
-  </si>
-  <si>
-    <t>[8, 3, 4, 9, 3, 7, 6]</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1717,10 +1742,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
@@ -2153,7 +2178,7 @@
         <v>131</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>132</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="33" x14ac:dyDescent="0.3">
@@ -2164,10 +2189,10 @@
         <v>4</v>
       </c>
       <c r="C4" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>133</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>134</v>
       </c>
       <c r="G4" t="s">
         <v>126</v>
@@ -2181,10 +2206,10 @@
         <v>5</v>
       </c>
       <c r="C5" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>135</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -2195,10 +2220,10 @@
         <v>6</v>
       </c>
       <c r="C6" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="D6" s="11" t="s">
         <v>137</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="33" x14ac:dyDescent="0.3">
@@ -2209,10 +2234,10 @@
         <v>7</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>140</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="33" x14ac:dyDescent="0.3">
@@ -2223,10 +2248,10 @@
         <v>8</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="2" t="s">
@@ -2241,10 +2266,10 @@
         <v>9</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>144</v>
+        <v>324</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>107</v>
@@ -2261,10 +2286,10 @@
         <v>10</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>108</v>
@@ -2281,10 +2306,10 @@
         <v>11</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>109</v>
@@ -2301,10 +2326,10 @@
         <v>12</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>150</v>
+        <v>303</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="2" t="s">
@@ -2319,10 +2344,10 @@
         <v>13</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>113</v>
@@ -2339,10 +2364,10 @@
         <v>14</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>114</v>
@@ -2359,10 +2384,10 @@
         <v>15</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="2" t="s">
@@ -2377,10 +2402,10 @@
         <v>16</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>115</v>
@@ -2397,10 +2422,10 @@
         <v>17</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>119</v>
@@ -2417,10 +2442,10 @@
         <v>18</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="2" t="s">
@@ -2435,10 +2460,10 @@
         <v>19</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>123</v>
@@ -2455,10 +2480,10 @@
         <v>20</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="2" t="s">
@@ -2473,10 +2498,10 @@
         <v>21</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>124</v>
@@ -2493,10 +2518,10 @@
         <v>22</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="49.5" x14ac:dyDescent="0.3">
@@ -2507,10 +2532,10 @@
         <v>23</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="G23" t="s">
         <v>125</v>
@@ -2524,10 +2549,10 @@
         <v>24</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="49.5" x14ac:dyDescent="0.3">
@@ -2538,10 +2563,10 @@
         <v>25</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="49.5" x14ac:dyDescent="0.3">
@@ -2552,10 +2577,10 @@
         <v>26</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="G26" s="7"/>
       <c r="H26" s="7"/>
@@ -2570,10 +2595,10 @@
         <v>27</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="G27" s="7"/>
       <c r="H27" s="8"/>
@@ -2588,10 +2613,10 @@
         <v>28</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="G28" s="7"/>
       <c r="H28" s="8"/>
@@ -2606,10 +2631,10 @@
         <v>29</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="G29" s="7"/>
       <c r="H29" s="8"/>
@@ -2624,10 +2649,10 @@
         <v>30</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="G30" s="7"/>
       <c r="H30" s="8"/>
@@ -2642,10 +2667,10 @@
         <v>31</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="G31" s="7"/>
       <c r="H31" s="8"/>
@@ -2660,10 +2685,10 @@
         <v>32</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>189</v>
+        <v>312</v>
       </c>
       <c r="G32" s="7"/>
       <c r="H32" s="8"/>
@@ -2678,10 +2703,10 @@
         <v>33</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>191</v>
+        <v>310</v>
       </c>
       <c r="G33" s="7"/>
       <c r="H33" s="8"/>
@@ -2696,10 +2721,10 @@
         <v>34</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="G34" s="7"/>
       <c r="H34" s="8"/>
@@ -2714,10 +2739,10 @@
         <v>35</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>195</v>
+        <v>317</v>
       </c>
       <c r="G35" s="7"/>
       <c r="H35" s="8"/>
@@ -2732,10 +2757,10 @@
         <v>36</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>197</v>
+        <v>315</v>
       </c>
       <c r="G36" s="7"/>
       <c r="H36" s="8"/>
@@ -2750,10 +2775,10 @@
         <v>37</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="G37" s="7"/>
       <c r="H37" s="8"/>
@@ -2768,10 +2793,10 @@
         <v>38</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="G38" s="7"/>
       <c r="H38" s="8"/>
@@ -2786,10 +2811,10 @@
         <v>39</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="G39" s="7"/>
       <c r="H39" s="8"/>
@@ -2804,10 +2829,10 @@
         <v>40</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="G40" s="7"/>
       <c r="H40" s="8"/>
@@ -2822,10 +2847,10 @@
         <v>41</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="G41" s="7"/>
       <c r="H41" s="8"/>
@@ -2840,10 +2865,10 @@
         <v>42</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="G42" s="7"/>
       <c r="H42" s="8"/>
@@ -2858,10 +2883,10 @@
         <v>43</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="G43" s="7"/>
       <c r="H43" s="8"/>
@@ -2876,10 +2901,10 @@
         <v>44</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>213</v>
+        <v>318</v>
       </c>
       <c r="G44" s="7"/>
       <c r="H44" s="8"/>
@@ -2894,10 +2919,10 @@
         <v>45</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="G45" s="7"/>
       <c r="H45" s="8"/>
@@ -2912,10 +2937,10 @@
         <v>46</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="G46" s="7"/>
       <c r="H46" s="8"/>
@@ -2930,10 +2955,10 @@
         <v>47</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="G47" s="7"/>
       <c r="H47" s="8"/>
@@ -2948,10 +2973,10 @@
         <v>48</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="G48" s="7"/>
       <c r="H48" s="8"/>
@@ -2966,10 +2991,10 @@
         <v>49</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="G49" s="7"/>
       <c r="H49" s="8"/>
@@ -2984,10 +3009,10 @@
         <v>50</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="G50" s="7"/>
       <c r="H50" s="8"/>
@@ -3002,10 +3027,10 @@
         <v>51</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="G51" s="7"/>
       <c r="H51" s="8"/>
@@ -3020,10 +3045,10 @@
         <v>52</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="G52" s="7"/>
       <c r="H52" s="8"/>
@@ -3038,10 +3063,10 @@
         <v>53</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="G53" s="7"/>
       <c r="H53" s="8"/>
@@ -3056,10 +3081,10 @@
         <v>54</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>233</v>
+        <v>320</v>
       </c>
       <c r="G54" s="7"/>
       <c r="H54" s="8"/>
@@ -3074,10 +3099,10 @@
         <v>55</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>235</v>
+        <v>327</v>
       </c>
       <c r="G55" s="7"/>
       <c r="H55" s="8"/>
@@ -3092,10 +3117,10 @@
         <v>56</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>237</v>
+        <v>325</v>
       </c>
       <c r="G56" s="7"/>
       <c r="H56" s="8"/>
@@ -3110,10 +3135,10 @@
         <v>57</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="G57" s="7"/>
       <c r="H57" s="8"/>
@@ -3128,10 +3153,10 @@
         <v>58</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="G58" s="7"/>
       <c r="H58" s="8"/>
@@ -3146,10 +3171,10 @@
         <v>59</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G59" s="7"/>
       <c r="H59" s="8"/>
@@ -3164,10 +3189,10 @@
         <v>60</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>245</v>
+        <v>316</v>
       </c>
       <c r="G60" s="7"/>
       <c r="H60" s="8"/>
@@ -3182,10 +3207,10 @@
         <v>61</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="G61" s="7"/>
       <c r="H61" s="8"/>
@@ -3200,10 +3225,10 @@
         <v>62</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="G62" s="7"/>
       <c r="H62" s="8"/>
@@ -3218,10 +3243,10 @@
         <v>63</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="G63" s="7"/>
       <c r="H63" s="8"/>
@@ -3236,10 +3261,10 @@
         <v>64</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="G64" s="7"/>
       <c r="H64" s="8"/>
@@ -3254,10 +3279,10 @@
         <v>65</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>255</v>
+        <v>322</v>
       </c>
       <c r="G65" s="7"/>
       <c r="H65" s="8"/>
@@ -3272,10 +3297,10 @@
         <v>66</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="G66" s="7"/>
       <c r="H66" s="8"/>
@@ -3290,10 +3315,10 @@
         <v>67</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="G67" s="7"/>
       <c r="H67" s="8"/>
@@ -3308,10 +3333,10 @@
         <v>68</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="G68" s="7"/>
       <c r="H68" s="8"/>
@@ -3326,10 +3351,10 @@
         <v>69</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>263</v>
+        <v>323</v>
       </c>
       <c r="G69" s="7"/>
       <c r="H69" s="8"/>
@@ -3344,10 +3369,10 @@
         <v>70</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="G70" s="7"/>
       <c r="H70" s="8"/>
@@ -3362,10 +3387,10 @@
         <v>71</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="G71" s="7"/>
       <c r="H71" s="8"/>
@@ -3380,10 +3405,10 @@
         <v>72</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="G72" s="7"/>
       <c r="H72" s="8"/>
@@ -3398,10 +3423,10 @@
         <v>73</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="G73" s="7"/>
       <c r="H73" s="8"/>
@@ -3416,10 +3441,10 @@
         <v>74</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="G74" s="7"/>
       <c r="H74" s="8"/>
@@ -3434,10 +3459,10 @@
         <v>75</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="G75" s="7"/>
       <c r="H75" s="8"/>
@@ -3452,10 +3477,10 @@
         <v>76</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>277</v>
+        <v>307</v>
       </c>
       <c r="G76" s="7"/>
       <c r="H76" s="8"/>
@@ -3470,10 +3495,10 @@
         <v>77</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>278</v>
+        <v>262</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>279</v>
+        <v>263</v>
       </c>
       <c r="G77" s="7"/>
       <c r="H77" s="8"/>
@@ -3488,10 +3513,10 @@
         <v>78</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>280</v>
+        <v>264</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>281</v>
+        <v>265</v>
       </c>
       <c r="G78" s="7"/>
       <c r="H78" s="8"/>
@@ -3506,10 +3531,10 @@
         <v>79</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>282</v>
+        <v>266</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>283</v>
+        <v>321</v>
       </c>
       <c r="G79" s="7"/>
       <c r="H79" s="8"/>
@@ -3524,10 +3549,10 @@
         <v>80</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="G80" s="7"/>
       <c r="H80" s="8"/>
@@ -3542,10 +3567,10 @@
         <v>81</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="G81" s="7"/>
       <c r="H81" s="8"/>
@@ -3560,10 +3585,10 @@
         <v>82</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="G82" s="7"/>
       <c r="H82" s="8"/>
@@ -3578,10 +3603,10 @@
         <v>83</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>290</v>
+        <v>273</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>291</v>
+        <v>274</v>
       </c>
       <c r="G83" s="7"/>
       <c r="H83" s="8"/>
@@ -3596,10 +3621,10 @@
         <v>84</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="G84" s="7"/>
       <c r="H84" s="8"/>
@@ -3614,10 +3639,10 @@
         <v>85</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="G85" s="7"/>
       <c r="H85" s="8"/>
@@ -3632,10 +3657,10 @@
         <v>86</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="G86" s="7"/>
       <c r="H86" s="8"/>
@@ -3650,10 +3675,10 @@
         <v>87</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="D87" s="11" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="G87" s="7"/>
       <c r="H87" s="8"/>
@@ -3668,10 +3693,10 @@
         <v>88</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="G88" s="7"/>
       <c r="H88" s="8"/>
@@ -3686,10 +3711,10 @@
         <v>89</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>302</v>
+        <v>283</v>
       </c>
       <c r="D89" s="11" t="s">
-        <v>303</v>
+        <v>284</v>
       </c>
       <c r="G89" s="7"/>
       <c r="H89" s="8"/>
@@ -3704,10 +3729,10 @@
         <v>90</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>304</v>
+        <v>285</v>
       </c>
       <c r="D90" s="11" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="G90" s="7"/>
       <c r="H90" s="8"/>
@@ -3722,10 +3747,10 @@
         <v>91</v>
       </c>
       <c r="C91" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="D91" s="11" t="s">
         <v>306</v>
-      </c>
-      <c r="D91" s="11" t="s">
-        <v>307</v>
       </c>
       <c r="G91" s="7"/>
       <c r="H91" s="8"/>
@@ -3740,10 +3765,10 @@
         <v>92</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>308</v>
+        <v>287</v>
       </c>
       <c r="D92" s="11" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="G92" s="7"/>
       <c r="H92" s="8"/>
@@ -3758,10 +3783,10 @@
         <v>93</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="D93" s="11" t="s">
-        <v>311</v>
+        <v>289</v>
       </c>
       <c r="G93" s="7"/>
       <c r="H93" s="8"/>
@@ -3776,10 +3801,10 @@
         <v>94</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>312</v>
+        <v>290</v>
       </c>
       <c r="D94" s="11" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="G94" s="7"/>
       <c r="H94" s="8"/>
@@ -3794,10 +3819,10 @@
         <v>95</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>314</v>
+        <v>292</v>
       </c>
       <c r="D95" s="11" t="s">
-        <v>315</v>
+        <v>293</v>
       </c>
       <c r="G95" s="7"/>
       <c r="H95" s="8"/>
@@ -3812,10 +3837,10 @@
         <v>96</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>316</v>
+        <v>294</v>
       </c>
       <c r="D96" s="11" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="G96" s="7"/>
       <c r="H96" s="8"/>
@@ -3830,10 +3855,10 @@
         <v>97</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>318</v>
+        <v>295</v>
       </c>
       <c r="D97" s="11" t="s">
-        <v>319</v>
+        <v>296</v>
       </c>
       <c r="G97" s="7"/>
       <c r="H97" s="8"/>
@@ -3848,10 +3873,10 @@
         <v>98</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>320</v>
+        <v>297</v>
       </c>
       <c r="D98" s="11" t="s">
-        <v>321</v>
+        <v>298</v>
       </c>
       <c r="G98" s="7"/>
       <c r="H98" s="8"/>
@@ -3866,10 +3891,10 @@
         <v>99</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>322</v>
+        <v>299</v>
       </c>
       <c r="D99" s="11" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
       <c r="G99" s="7"/>
       <c r="H99" s="8"/>
@@ -3884,10 +3909,10 @@
         <v>100</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>324</v>
+        <v>300</v>
       </c>
       <c r="D100" s="11" t="s">
-        <v>325</v>
+        <v>301</v>
       </c>
       <c r="G100" s="7"/>
       <c r="H100" s="8"/>
@@ -3902,10 +3927,10 @@
         <v>101</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>326</v>
+        <v>302</v>
       </c>
       <c r="D101" s="11" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="G101" s="7"/>
       <c r="H101" s="8"/>

--- a/excel/TRT_Word_KOR.xlsx
+++ b/excel/TRT_Word_KOR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\classification-main\classification-main\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A4D3305-C15A-4AB6-94B0-D943EEB14878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9A66B20-277A-491B-BE92-4D7AB1FF8164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4815" yWindow="3195" windowWidth="28800" windowHeight="15255" xr2:uid="{74BD6AE7-1D9C-4ADB-9E4F-52195803F6A8}"/>
+    <workbookView xWindow="53325" yWindow="3330" windowWidth="20775" windowHeight="15315" xr2:uid="{74BD6AE7-1D9C-4ADB-9E4F-52195803F6A8}"/>
   </bookViews>
   <sheets>
     <sheet name="TRT_Word_KOR" sheetId="1" r:id="rId1"/>
